--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$17</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="168">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -309,6 +312,9 @@
     <t>Extension.url</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">uri
 </t>
   </si>
@@ -349,6 +355,184 @@
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
+  </si>
+  <si>
+    <t>Extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Extension.value[x].coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Extension.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Extension.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Extension.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/AtElgaEmedCodeSystemDosageCategory</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Extension.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Extension.value[x].coding.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Extension.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Extension.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Extension.value[x].text</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: TODO</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
 </sst>
 </file>
@@ -477,6 +661,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -666,13 +865,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AK17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.80078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="16.80078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.0546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.0546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -683,7 +882,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="196.6875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -700,11 +899,11 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="20.5390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="39.890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,7 +1019,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -923,7 +1122,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>81</v>
       </c>
@@ -1026,7 +1225,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>88</v>
       </c>
@@ -1148,7 +1347,7 @@
         <v>82</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>21</v>
@@ -1157,16 +1356,16 @@
         <v>21</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1231,15 +1430,15 @@
         <v>21</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1253,7 +1452,7 @@
         <v>82</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>21</v>
@@ -1262,13 +1461,13 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1295,13 +1494,13 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>21</v>
@@ -1319,7 +1518,7 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -1331,13 +1530,1190 @@
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" hidden="true">
+      <c r="A7" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" hidden="true">
+      <c r="A8" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="O9" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="P9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" hidden="true">
+      <c r="A10" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK10" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" hidden="true">
+      <c r="A11" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="P14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
+      <c r="A16" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="P16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="17" hidden="true">
+      <c r="A17" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="O17" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="P17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AK17">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI16">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -350,7 +350,7 @@
     <t>Code für die Art der Dosierung</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/AtElgaEmedValueSetDosageCategory</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/at-elga-emed-valueset-dosagecategory-vs</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -422,7 +422,7 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/AtElgaEmedCodeSystemDosageCategory</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/CodeSystem/at-elga-emed-codesystem-dosagecategory-cs</t>
   </si>
   <si>
     <t>Coding.system</t>
@@ -893,7 +893,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="24.9921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.00390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.65234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -517,7 +517,7 @@
     <t>Extension.value[x].text</t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>Plain text representation of the concept</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-extension-dosage-category.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
